--- a/src/grafs_e/data/scenario_region/Linear/France.xlsx
+++ b/src/grafs_e/data/scenario_region/Linear/France.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -786,23 +786,6 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Methanisation</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>GWh</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2021 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -1689,7 +1672,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1745,37 +1728,41 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Weight export</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
+          <t>N recycling rate of human excretion in urban area</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Weight for the optimization model</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Weight energy</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
+          <t>N recycling rate of human excretion in rural area</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Weight for the optimization model</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1792,7 +1779,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1809,41 +1796,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1860,7 +1847,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1877,7 +1864,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1894,7 +1881,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1911,41 +1898,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1962,7 +1949,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1979,7 +1966,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1996,7 +1983,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2013,7 +2000,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2030,7 +2017,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2047,7 +2034,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2064,7 +2051,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2081,7 +2068,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2098,7 +2085,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2115,7 +2102,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2132,7 +2119,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2149,7 +2136,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2166,7 +2153,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2183,7 +2170,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2200,7 +2187,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2217,7 +2204,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2234,7 +2221,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2251,7 +2238,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2268,7 +2255,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2285,7 +2272,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2302,7 +2289,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2319,12 +2306,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2336,12 +2323,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2353,7 +2340,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2370,7 +2357,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2387,7 +2374,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2404,7 +2391,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2421,41 +2408,41 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2472,7 +2459,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2489,7 +2476,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2506,7 +2493,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2523,12 +2510,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>kg/LU</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2540,12 +2527,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>kg/LU</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2557,7 +2544,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Caprines dairy productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2574,7 +2561,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Poultry dairy productivity</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2583,40 +2570,6 @@
         </is>
       </c>
       <c r="E55" t="inlineStr">
-        <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Caprines dairy productivity</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Poultry dairy productivity</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>kg/LU</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>

--- a/src/grafs_e/data/scenario_region/Linear/France.xlsx
+++ b/src/grafs_e/data/scenario_region/Linear/France.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,23 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Methanisation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2021 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -1672,7 +1689,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1728,41 +1745,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+          <t>Weight export</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+          <t>Weight energy</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1779,7 +1792,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1796,41 +1809,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1847,7 +1860,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1864,7 +1877,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1881,7 +1894,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1898,41 +1911,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1949,7 +1962,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1966,7 +1979,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1983,7 +1996,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2000,7 +2013,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2017,7 +2030,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2034,7 +2047,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2051,7 +2064,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2068,7 +2081,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2085,7 +2098,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2102,7 +2115,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2119,7 +2132,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2136,7 +2149,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2153,7 +2166,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2170,7 +2183,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2187,7 +2200,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2204,7 +2217,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2221,7 +2234,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2238,7 +2251,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2255,7 +2268,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2272,7 +2285,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2289,7 +2302,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2306,12 +2319,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2323,12 +2336,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2340,7 +2353,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2357,7 +2370,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2374,7 +2387,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2391,7 +2404,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2408,41 +2421,41 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2459,7 +2472,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2476,7 +2489,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2493,7 +2506,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2510,12 +2523,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2527,12 +2540,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2544,7 +2557,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2561,15 +2574,49 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Ovines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>

--- a/src/grafs_e/data/scenario_region/Linear/France.xlsx
+++ b/src/grafs_e/data/scenario_region/Linear/France.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,23 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>No business as usual: computed with optimization model to fertilize all crops</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Methaniser production</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GWh/yr</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Regional 2021 data mapped on 2006 33 region plant production. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -1672,7 +1689,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1728,24 +1745,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+          <t>Weight energy</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1762,7 +1777,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1779,7 +1794,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1796,24 +1811,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1830,7 +1845,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1847,7 +1862,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1864,7 +1879,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1881,7 +1896,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1898,24 +1913,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1932,7 +1947,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1949,7 +1964,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1966,7 +1981,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1983,7 +1998,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2000,7 +2015,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2017,7 +2032,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2034,7 +2049,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2051,7 +2066,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2068,7 +2083,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2085,7 +2100,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2102,7 +2117,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2119,7 +2134,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2136,7 +2151,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2153,7 +2168,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2170,7 +2185,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2187,7 +2202,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2204,7 +2219,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2221,7 +2236,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2238,7 +2253,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2255,7 +2270,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2272,7 +2287,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2289,7 +2304,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2306,12 +2321,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2323,7 +2338,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2340,7 +2355,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2357,7 +2372,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2374,7 +2389,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2391,7 +2406,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2408,24 +2423,24 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2442,7 +2457,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2459,7 +2474,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2476,7 +2491,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2493,7 +2508,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2510,12 +2525,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2527,7 +2542,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2544,7 +2559,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2561,15 +2576,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>

--- a/src/grafs_e/data/scenario_region/Linear/France.xlsx
+++ b/src/grafs_e/data/scenario_region/Linear/France.xlsx
@@ -1652,7 +1652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -1760,24 +1760,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+          <t>Weight methaniser input</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>25</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Weight for the optimization model</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1794,7 +1792,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1811,7 +1809,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1828,24 +1826,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1862,7 +1860,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1879,7 +1877,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1896,7 +1894,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1913,7 +1911,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1930,24 +1928,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1964,7 +1962,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1981,7 +1979,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1998,7 +1996,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2015,7 +2013,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2032,7 +2030,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2049,7 +2047,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2066,7 +2064,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2083,7 +2081,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2100,7 +2098,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2117,7 +2115,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2134,7 +2132,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2151,7 +2149,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2168,7 +2166,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2185,7 +2183,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2202,7 +2200,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2219,7 +2217,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2236,7 +2234,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2253,7 +2251,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2270,7 +2268,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2287,7 +2285,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2304,7 +2302,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2321,7 +2319,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2338,12 +2336,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2355,7 +2353,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2372,7 +2370,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2389,7 +2387,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2406,7 +2404,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2423,7 +2421,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2440,24 +2438,24 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2474,7 +2472,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2491,7 +2489,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2508,7 +2506,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2525,7 +2523,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2542,12 +2540,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2559,7 +2557,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2576,7 +2574,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2593,17 +2591,134 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>Caprines dairy productivity</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>kg/LU</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Poultry dairy productivity</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>kg/LU</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Share of crop residues in methaniser</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Share of green waste in methaniser</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Share of dedicated culture in methaniser</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Share of animal food industry in methaniser</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Share of livestock effluent in methaniser</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
         </is>
       </c>
     </row>

--- a/src/grafs_e/data/scenario_region/Linear/France.xlsx
+++ b/src/grafs_e/data/scenario_region/Linear/France.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -605,24 +605,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Urban population</t>
+          <t>Total per capita protein ingestion</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN/cap/yr</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Logistic</t>
+          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Total per capita protein ingestion</t>
+          <t>Vegetal per capita protein ingestion</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vegetal per capita protein ingestion</t>
+          <t>Edible animal per capita protein ingestion (excl fish)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -656,24 +656,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Edible animal per capita protein ingestion (excl fish)</t>
+          <t>Arable area</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>kgN/cap/yr</t>
+          <t>ha</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
+          <t>Historical trend</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arable area</t>
+          <t>Permanent grassland area</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -690,24 +690,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Permanent grassland area</t>
+          <t>Import of vegetal pdcts</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ha</t>
+          <t>ktN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Historical trend</t>
+          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Import of vegetal pdcts</t>
+          <t>Export of vegetal pdcts</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -724,41 +724,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Export of vegetal pdcts</t>
+          <t>Total LU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ktN</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2006 data. Used as a goal but may be adjusted according to territory situation</t>
+          <t>Historical trend, see prop for each livestock in technical sheet</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Total LU</t>
+          <t>Synth N fertilizer application to cropland</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>kgN/ha/yr</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Historical trend, see prop for each livestock in technical sheet</t>
+          <t>No business as usual: computed with optimization model to fertilize all crops</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Synth N fertilizer application to cropland</t>
+          <t>Synth N fertilizer application to grassland</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -775,32 +775,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Synth N fertilizer application to grassland</t>
+          <t>Methaniser production</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>kgN/ha/yr</t>
+          <t>GWh/yr</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>No business as usual: computed with optimization model to fertilize all crops</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Methaniser production</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>GWh/yr</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
         <is>
           <t>Regional 2021 data mapped on 2006 33 region plant production. Used as a goal but may be adjusted according to territory situation</t>
         </is>
@@ -1652,7 +1635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -1681,6 +1664,11 @@
           <t>Comment</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1696,6 +1684,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1711,6 +1702,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1726,6 +1720,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1741,6 +1738,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1756,6 +1756,9 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1771,28 +1774,31 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in urban area</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+          <t>Urban population</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Logistic</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>%</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Taken as the last historical value</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N recycling rate of human excretion in rural area</t>
+          <t>N recycling rate of human excretion in urban area</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1804,12 +1810,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
+          <t>N recycling rate of human excretion in rural area</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1821,12 +1830,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
+          <t>NH3 volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1838,29 +1850,35 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F11" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kgN excreted by bovines LU</t>
+          <t>Indirect N2O volatilization coefficient for synthetic nitrogen</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>kgN</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Historical trend</t>
-        </is>
+          <t>Taken as the last historical value</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kgN excreted by equines LU</t>
+          <t>kgN excreted by bovines LU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1872,12 +1890,15 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kgN excreted by caprines LU</t>
+          <t>kgN excreted by equines LU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1889,12 +1910,15 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F14" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kgN excreted by ovines LU</t>
+          <t>kgN excreted by caprines LU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1906,12 +1930,15 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F15" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kgN excreted by porcines LU</t>
+          <t>kgN excreted by ovines LU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1923,12 +1950,15 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F16" t="n">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kgN excreted by poultry LU</t>
+          <t>kgN excreted by porcines LU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1940,29 +1970,35 @@
         <is>
           <t>Historical trend</t>
         </is>
+      </c>
+      <c r="F17" t="n">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bovines % excretion on grassland</t>
+          <t>kgN excreted by poultry LU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kgN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Taken as the last historical value</t>
-        </is>
+          <t>Historical trend</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as litter manure</t>
+          <t>Bovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1974,12 +2010,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F19" t="n">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as other manure</t>
+          <t>Bovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1991,12 +2030,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F20" t="n">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bovines % excretion in the barn as slurry</t>
+          <t>Bovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2008,12 +2050,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F21" t="n">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ovines % excretion on grassland</t>
+          <t>Bovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2025,12 +2070,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F22" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as litter manure</t>
+          <t>Ovines % excretion on grassland</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2042,12 +2090,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F23" t="n">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as other manure</t>
+          <t>Ovines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2059,12 +2110,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F24" t="n">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ovines % excretion in the barn as slurry</t>
+          <t>Ovines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2076,12 +2130,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F25" t="n">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equines % excretion on grassland</t>
+          <t>Ovines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2093,12 +2150,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F26" t="n">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as litter manure</t>
+          <t>Equines % excretion on grassland</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2110,12 +2170,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F27" t="n">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as other manure</t>
+          <t>Equines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2127,12 +2190,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F28" t="n">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Equines % excretion in the barn as slurry</t>
+          <t>Equines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2144,12 +2210,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F29" t="n">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Caprines % excretion on grassland</t>
+          <t>Equines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2161,12 +2230,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F30" t="n">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as litter manure</t>
+          <t>Caprines % excretion on grassland</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2178,12 +2250,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F31" t="n">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as other manure</t>
+          <t>Caprines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2195,12 +2270,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F32" t="n">
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Caprines % excretion in the barn as slurry</t>
+          <t>Caprines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2212,12 +2290,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F33" t="n">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Porcines % excretion on grassland</t>
+          <t>Caprines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2229,12 +2310,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F34" t="n">
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as litter manure</t>
+          <t>Porcines % excretion on grassland</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2246,12 +2330,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F35" t="n">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as other manure</t>
+          <t>Porcines % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2263,12 +2350,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F36" t="n">
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Porcines % excretion in the barn as slurry</t>
+          <t>Porcines % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2280,12 +2370,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F37" t="n">
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poultry % excretion on grassland</t>
+          <t>Porcines % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2297,12 +2390,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F38" t="n">
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as litter manure</t>
+          <t>Poultry % excretion on grassland</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2314,12 +2410,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F39" t="n">
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as other manure</t>
+          <t>Poultry % excretion in the barn as litter manure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,12 +2430,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F40" t="n">
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Poultry % excretion in the barn as slurry</t>
+          <t>Poultry % excretion in the barn as other manure</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2348,29 +2450,35 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F41" t="n">
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bovines LU</t>
+          <t>Poultry % excretion in the barn as slurry</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>prop</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F42" t="n">
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ovines LU</t>
+          <t>Bovines LU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2382,12 +2490,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F43" t="n">
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Caprines LU</t>
+          <t>Ovines LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2399,12 +2510,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F44" t="n">
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Equines LU</t>
+          <t>Caprines LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2416,12 +2530,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F45" t="n">
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Porcines LU</t>
+          <t>Equines LU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2433,12 +2550,15 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F46" t="n">
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Poultry LU</t>
+          <t>Porcines LU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2450,29 +2570,35 @@
         <is>
           <t>Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F47" t="n">
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bovines productivity</t>
+          <t>Poultry LU</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>kgcarcass/LU</t>
+          <t>prop</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
-        </is>
+          <t>Taken as the last historical value</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ovines productivity</t>
+          <t>Bovines productivity</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2484,12 +2610,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F49" t="n">
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Caprines productivity</t>
+          <t>Ovines productivity</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2501,12 +2630,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F50" t="n">
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Equines productivity</t>
+          <t>Caprines productivity</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2518,12 +2650,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F51" t="n">
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Porcines productivity</t>
+          <t>Equines productivity</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2535,12 +2670,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F52" t="n">
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Poultry productivity</t>
+          <t>Porcines productivity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2552,29 +2690,35 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F53" t="n">
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bovines dairy productivity</t>
+          <t>Poultry productivity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>kg/LU</t>
+          <t>kgcarcass/LU</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F54" t="n">
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ovines dairy productivity</t>
+          <t>Bovines dairy productivity</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2586,12 +2730,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F55" t="n">
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Caprines dairy productivity</t>
+          <t>Ovines dairy productivity</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2603,12 +2750,15 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F56" t="n">
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Poultry dairy productivity</t>
+          <t>Caprines dairy productivity</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2620,32 +2770,35 @@
         <is>
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
+      </c>
+      <c r="F57" t="n">
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Share of crop residues in methaniser</t>
+          <t>Poultry dairy productivity</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>0.06</v>
+          <t>kg/LU</t>
+        </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Adapted from ONRB data</t>
-        </is>
+          <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Share of green waste in methaniser</t>
+          <t>Share of crop residues in methaniser</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2654,18 +2807,21 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>Adapted from ONRB data</t>
         </is>
+      </c>
+      <c r="F59" t="n">
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Share of dedicated culture in methaniser</t>
+          <t>Share of green waste in methaniser</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2674,18 +2830,21 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>Adapted from ONRB data</t>
         </is>
+      </c>
+      <c r="F60" t="n">
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Share of animal food industry in methaniser</t>
+          <t>Share of dedicated culture in methaniser</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2694,32 +2853,61 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>Adapted from ONRB data</t>
         </is>
+      </c>
+      <c r="F61" t="n">
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>Share of animal food industry in methaniser</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>prop</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Adapted from ONRB data</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>Share of livestock effluent in methaniser</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>prop</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="C63" t="n">
         <v>0.79</v>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Adapted from ONRB data</t>
         </is>
+      </c>
+      <c r="F63" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/src/grafs_e/data/scenario_region/Linear/France.xlsx
+++ b/src/grafs_e/data/scenario_region/Linear/France.xlsx
@@ -800,38 +800,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Crops</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Area proportion (%)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Enforce Area</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>r2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Straw to Grain Ratio</t>
         </is>
       </c>
     </row>
@@ -856,6 +861,9 @@
       <c r="F2" t="n">
         <v>0.95</v>
       </c>
+      <c r="G2" t="n">
+        <v>0.06900000000000001</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -878,6 +886,9 @@
       <c r="F3" t="n">
         <v>1</v>
       </c>
+      <c r="G3" t="n">
+        <v>0.076</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -900,6 +911,9 @@
       <c r="F4" t="n">
         <v>0.97</v>
       </c>
+      <c r="G4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -922,11 +936,14 @@
       <c r="F5" t="n">
         <v>1</v>
       </c>
+      <c r="G5" t="n">
+        <v>0.055</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Grain maize</t>
+          <t>Maize</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -944,6 +961,9 @@
       <c r="F6" t="n">
         <v>0.9399999999999999</v>
       </c>
+      <c r="G6" t="n">
+        <v>0.07199999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -966,6 +986,9 @@
       <c r="F7" t="n">
         <v>0.97</v>
       </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -988,279 +1011,318 @@
       <c r="F8" t="n">
         <v>0.99</v>
       </c>
+      <c r="G8" t="n">
+        <v>0.073</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Straw</t>
+          <t>Rapeseed</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>8.494545271436346</v>
       </c>
       <c r="C9" t="b">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="E9" t="n">
-        <v>123.09</v>
+        <v>126.02</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
+      </c>
+      <c r="G9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rapeseed</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8.494545271436346</v>
+        <v>3.725358950618109</v>
       </c>
       <c r="C10" t="b">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="E10" t="n">
-        <v>126.02</v>
+        <v>45.89</v>
       </c>
       <c r="F10" t="n">
-        <v>0.84</v>
+        <v>0.76</v>
+      </c>
+      <c r="G10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Soybean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.725358950618109</v>
+        <v>0.4284678107259858</v>
       </c>
       <c r="C11" t="b">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.58</v>
+        <v>0.79</v>
       </c>
       <c r="E11" t="n">
-        <v>45.89</v>
+        <v>179.8</v>
       </c>
       <c r="F11" t="n">
-        <v>0.76</v>
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Soybean</t>
+          <t>Other oil crops</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4284678107259858</v>
+        <v>0.1147760337501906</v>
       </c>
       <c r="C12" t="b">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>179.8</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.93</v>
+      </c>
+      <c r="G12" t="n">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Other oil crops</t>
+          <t>Horse beans and faba beans</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1147760337501906</v>
+        <v>0.4234276777025442</v>
       </c>
       <c r="C13" t="b">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="E13" t="n">
-        <v>70.06999999999999</v>
+        <v>180.34</v>
       </c>
       <c r="F13" t="n">
-        <v>0.93</v>
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Horse beans and faba beans</t>
+          <t>Peas</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4234276777025442</v>
+        <v>0.7890350849691262</v>
       </c>
       <c r="C14" t="b">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="E14" t="n">
-        <v>180.34</v>
+        <v>181.75</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
+      <c r="G14" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Peas</t>
+          <t>Other protein crops</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7890350849691262</v>
+        <v>0.0297040126729066</v>
       </c>
       <c r="C15" t="b">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="E15" t="n">
-        <v>181.75</v>
+        <v>110.71</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
+      <c r="G15" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Other protein crops</t>
+          <t>Sugar beet</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0297040126729066</v>
+        <v>2.300538206533874</v>
       </c>
       <c r="C16" t="b">
         <v>0</v>
       </c>
       <c r="D16" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E16" t="n">
+        <v>156.87</v>
+      </c>
+      <c r="F16" t="n">
         <v>0.79</v>
       </c>
-      <c r="E16" t="n">
-        <v>110.71</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
+      <c r="G16" t="n">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sugar beet</t>
+          <t>Potatoes</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.300538206533874</v>
+        <v>0.9480987449948051</v>
       </c>
       <c r="C17" t="b">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.84</v>
+        <v>0.6</v>
       </c>
       <c r="E17" t="n">
-        <v>156.87</v>
+        <v>96.03</v>
       </c>
       <c r="F17" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
+      </c>
+      <c r="G17" t="n">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Potatoes</t>
+          <t>Other roots</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9480987449948051</v>
+        <v>0</v>
       </c>
       <c r="C18" t="b">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="E18" t="n">
-        <v>96.03</v>
+        <v>136.7</v>
       </c>
       <c r="F18" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
+      </c>
+      <c r="G18" t="n">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Other roots</t>
+          <t>Green peas</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.1299868387940301</v>
       </c>
       <c r="C19" t="b">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.57</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>136.7</v>
+        <v>70.28</v>
       </c>
       <c r="F19" t="n">
-        <v>0.79</v>
+        <v>0.98</v>
+      </c>
+      <c r="G19" t="n">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Green peas</t>
+          <t>Dry beans</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1299868387940301</v>
+        <v>0.02795804730940496</v>
       </c>
       <c r="C20" t="b">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="E20" t="n">
-        <v>70.28</v>
+        <v>152.71</v>
       </c>
       <c r="F20" t="n">
-        <v>0.98</v>
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dry beans</t>
+          <t>Green beans</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.02795804730940496</v>
+        <v>0.117623821915902</v>
       </c>
       <c r="C21" t="b">
         <v>0</v>
@@ -1269,60 +1331,69 @@
         <v>0.79</v>
       </c>
       <c r="E21" t="n">
-        <v>152.71</v>
+        <v>83.8</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
+      <c r="G21" t="n">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Green beans</t>
+          <t>Dry vegetables</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.117623821915902</v>
+        <v>0.11765772415597</v>
       </c>
       <c r="C22" t="b">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.79</v>
+        <v>0.97</v>
       </c>
       <c r="E22" t="n">
-        <v>83.8</v>
+        <v>165.27</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0.99</v>
+      </c>
+      <c r="G22" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dry vegetables</t>
+          <t>Dry fruits</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.11765772415597</v>
+        <v>0</v>
       </c>
       <c r="C23" t="b">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.97</v>
+        <v>0.75</v>
       </c>
       <c r="E23" t="n">
-        <v>165.27</v>
+        <v>36.85</v>
       </c>
       <c r="F23" t="n">
-        <v>0.99</v>
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dry fruits</t>
+          <t>Squash and melons</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1332,19 +1403,22 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.75</v>
+        <v>0.97</v>
       </c>
       <c r="E24" t="n">
-        <v>36.85</v>
+        <v>56.8</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>0.99</v>
+      </c>
+      <c r="G24" t="n">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Squash and melons</t>
+          <t>Cabbage</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1354,19 +1428,22 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.97</v>
+        <v>0.87</v>
       </c>
       <c r="E25" t="n">
-        <v>56.8</v>
+        <v>51.25</v>
       </c>
       <c r="F25" t="n">
-        <v>0.99</v>
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cabbage</t>
+          <t>Leaves vegetables</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1376,19 +1453,22 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0.87</v>
+        <v>0.97</v>
       </c>
       <c r="E26" t="n">
-        <v>51.25</v>
+        <v>33.43</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.03</v>
+      </c>
+      <c r="G26" t="n">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Leaves vegetables</t>
+          <t>Fruits</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1398,45 +1478,51 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.97</v>
+        <v>0.93</v>
       </c>
       <c r="E27" t="n">
-        <v>33.43</v>
+        <v>23.9</v>
       </c>
       <c r="F27" t="n">
-        <v>0.03</v>
+        <v>0.88</v>
+      </c>
+      <c r="G27" t="n">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Fruits</t>
+          <t>Olives</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.09402786282857881</v>
       </c>
       <c r="C28" t="b">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.93</v>
+        <v>0.75</v>
       </c>
       <c r="E28" t="n">
-        <v>23.9</v>
+        <v>14.11</v>
       </c>
       <c r="F28" t="n">
-        <v>0.88</v>
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Olives</t>
+          <t>Citrus</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09402786282857881</v>
+        <v>0</v>
       </c>
       <c r="C29" t="b">
         <v>0</v>
@@ -1445,183 +1531,185 @@
         <v>0.75</v>
       </c>
       <c r="E29" t="n">
-        <v>14.11</v>
+        <v>18.26</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Citrus</t>
+          <t>Hemp</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.0005254847210538927</v>
       </c>
       <c r="C30" t="b">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="E30" t="n">
-        <v>18.26</v>
+        <v>243.87</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.68</v>
+      </c>
+      <c r="G30" t="n">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Hemp</t>
+          <t>Flax</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0005254847210538927</v>
+        <v>0</v>
       </c>
       <c r="C31" t="b">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7</v>
+        <v>0.86</v>
       </c>
       <c r="E31" t="n">
-        <v>243.87</v>
+        <v>11.47</v>
       </c>
       <c r="F31" t="n">
-        <v>0.68</v>
+        <v>0.24</v>
+      </c>
+      <c r="G31" t="n">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Flax</t>
+          <t>Forage maize</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>9.152678157129605</v>
       </c>
       <c r="C32" t="b">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.86</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>11.47</v>
+        <v>336.7</v>
       </c>
       <c r="F32" t="n">
-        <v>0.24</v>
+        <v>0.98</v>
+      </c>
+      <c r="G32" t="n">
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Forage maize</t>
+          <t>Forage cabbages</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>9.152678157129605</v>
+        <v>0.0546706787533466</v>
       </c>
       <c r="C33" t="b">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="E33" t="n">
-        <v>336.7</v>
+        <v>130.65</v>
       </c>
       <c r="F33" t="n">
-        <v>0.98</v>
+        <v>0.83</v>
+      </c>
+      <c r="G33" t="n">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Forage cabbages</t>
+          <t>Alfalfa and clover</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0546706787533466</v>
+        <v>1.278639935284393</v>
       </c>
       <c r="C34" t="b">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0.98</v>
+        <v>0.62</v>
       </c>
       <c r="E34" t="n">
-        <v>130.65</v>
+        <v>213.13</v>
       </c>
       <c r="F34" t="n">
-        <v>0.83</v>
+        <v>0.99</v>
+      </c>
+      <c r="G34" t="n">
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alfalfa and clover</t>
+          <t>Non-legume temporary meadow</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.278639935284393</v>
+        <v>17.4220899530211</v>
       </c>
       <c r="C35" t="b">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="E35" t="n">
-        <v>213.13</v>
+        <v>329.52</v>
       </c>
       <c r="F35" t="n">
-        <v>0.99</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G35" t="n">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Non-legume temporary meadow</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>17.4220899530211</v>
+          <t xml:space="preserve">Natural meadow </t>
+        </is>
       </c>
       <c r="C36" t="b">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
       <c r="E36" t="n">
-        <v>329.52</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Natural meadow </t>
-        </is>
-      </c>
-      <c r="C37" t="b">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E37" t="n">
-        <v>95.93000000000001</v>
-      </c>
-      <c r="F37" t="n">
         <v>0.76</v>
+      </c>
+      <c r="G36" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1684,9 +1772,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1702,9 +1787,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1720,9 +1802,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1738,9 +1817,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1756,9 +1832,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1774,9 +1847,6 @@
           <t>Weight for the optimization model</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1811,9 +1881,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1831,9 +1898,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1851,9 +1915,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1871,9 +1932,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v/>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1891,9 +1949,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1911,9 +1966,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1931,9 +1983,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v/>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1951,9 +2000,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1971,9 +2017,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v/>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1991,9 +2034,6 @@
           <t>Historical trend</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2011,9 +2051,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,9 +2068,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v/>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2051,9 +2085,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v/>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2071,9 +2102,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v/>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2091,9 +2119,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2111,9 +2136,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2131,9 +2153,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v/>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2151,9 +2170,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v/>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2171,9 +2187,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v/>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2191,9 +2204,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v/>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2211,9 +2221,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v/>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2231,9 +2238,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v/>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2251,9 +2255,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2271,9 +2272,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v/>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2291,9 +2289,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v/>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2311,9 +2306,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v/>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2331,9 +2323,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v/>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2351,9 +2340,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v/>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2371,9 +2357,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v/>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2391,9 +2374,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v/>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2411,9 +2391,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v/>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2431,9 +2408,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v/>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2451,9 +2425,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v/>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2471,9 +2442,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v/>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2491,9 +2459,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v/>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2511,9 +2476,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v/>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2531,9 +2493,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v/>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2551,9 +2510,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v/>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2571,9 +2527,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v/>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2591,9 +2544,6 @@
           <t>Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v/>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2611,9 +2561,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v/>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2631,9 +2578,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v/>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2651,9 +2595,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v/>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2671,9 +2612,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F52" t="n">
-        <v/>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2691,9 +2629,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v/>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2711,9 +2646,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v/>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2731,9 +2663,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F55" t="n">
-        <v/>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2751,9 +2680,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F56" t="n">
-        <v/>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2771,9 +2697,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v/>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2791,9 +2714,6 @@
           <t>These groups are taken as a whole even if only a part is producing meat, milk or eggs. Taken as the last historical value</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v/>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2814,9 +2734,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F59" t="n">
-        <v/>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2837,9 +2754,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F60" t="n">
-        <v/>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2860,9 +2774,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v/>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2883,9 +2794,6 @@
           <t>Adapted from ONRB data</t>
         </is>
       </c>
-      <c r="F62" t="n">
-        <v/>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2905,9 +2813,6 @@
         <is>
           <t>Adapted from ONRB data</t>
         </is>
-      </c>
-      <c r="F63" t="n">
-        <v/>
       </c>
     </row>
   </sheetData>
